--- a/modules/40_q3/figures/editable/origin_templates/data/19_Si参数可辨识性气泡图.xlsx
+++ b/modules/40_q3/figures/editable/origin_templates/data/19_Si参数可辨识性气泡图.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据" sheetId="1" r:id="Rdc1b452140a64100"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据" sheetId="1" r:id="R5d1ce14204794e88"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,32 +13,21 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="4">
-    <x:numFmt numFmtId="200" formatCode="@"/>
-    <x:numFmt numFmtId="201" formatCode="0.0"/>
-    <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="0"/>
-  </x:numFmts>
-  <x:fonts count="4">
+  <x:fonts count="3">
     <x:font>
       <x:sz val="11"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF222222"/>
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
       <x:b/>
       <x:sz val="11"/>
       <x:color rgb="FFFFFFFF"/>
-      <x:name val="宋体"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="10"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Times New Roman"/>
-    </x:font>
-    <x:font>
-      <x:sz val="10"/>
-      <x:name val="Times New Roman"/>
+      <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
   <x:fills count="3">
@@ -54,181 +43,37 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="10">
+  <x:borders count="2">
     <x:border/>
     <x:border>
-      <x:right style="thin">
-        <x:color rgb="FFE7EEF5"/>
-      </x:right>
-      <x:bottom style="thin">
-        <x:color rgb="FFE7EEF5"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
       <x:left style="thin">
-        <x:color rgb="FFE7EEF5"/>
+        <x:color rgb="FFD9E2F3"/>
       </x:left>
       <x:right style="thin">
-        <x:color rgb="FFE7EEF5"/>
-      </x:right>
-      <x:bottom style="thin">
-        <x:color rgb="FFE7EEF5"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFE7EEF5"/>
-      </x:left>
-      <x:bottom style="thin">
-        <x:color rgb="FFE7EEF5"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:right style="thin">
-        <x:color rgb="FFE7EEF5"/>
+        <x:color rgb="FFD9E2F3"/>
       </x:right>
       <x:top style="thin">
-        <x:color rgb="FFE7EEF5"/>
+        <x:color rgb="FFD9E2F3"/>
       </x:top>
       <x:bottom style="thin">
-        <x:color rgb="FFE7EEF5"/>
+        <x:color rgb="FFD9E2F3"/>
       </x:bottom>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFE7EEF5"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FFE7EEF5"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FFE7EEF5"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFE7EEF5"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFE7EEF5"/>
-      </x:left>
-      <x:top style="thin">
-        <x:color rgb="FFE7EEF5"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFE7EEF5"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:right style="thin">
-        <x:color rgb="FFE7EEF5"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FFE7EEF5"/>
-      </x:top>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFE7EEF5"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FFE7EEF5"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FFE7EEF5"/>
-      </x:top>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFE7EEF5"/>
-      </x:left>
-      <x:top style="thin">
-        <x:color rgb="FFE7EEF5"/>
-      </x:top>
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="33">
+  <x:cellXfs count="7">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="202" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="202" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="203" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="203" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="0"/>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -432,112 +277,61 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="21" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="16" t="str">
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="6" t="str">
         <x:v>拟合方案(标签)</x:v>
       </x:c>
-      <x:c r="B1" s="17" t="str">
+      <x:c r="B1" s="6" t="str">
         <x:v>入射角(度)(X)</x:v>
       </x:c>
-      <x:c r="C1" s="17" t="str">
+      <x:c r="C1" s="6" t="str">
         <x:v>RMSE(百分点)(Y)</x:v>
       </x:c>
-      <x:c r="D1" s="17" t="str">
+      <x:c r="D1" s="6" t="str">
         <x:v>Jacobian条件数(气泡大小)</x:v>
       </x:c>
-      <x:c r="E1" s="18" t="str">
+      <x:c r="E1" s="6" t="str">
         <x:v>触边参数个数(颜色分组)</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="25" t="str">
-        <x:v>10度双光束</x:v>
-      </x:c>
-      <x:c r="B2" s="27" t="n">
+      <x:c r="A2" s="2" t="str">
+        <x:v>10度Airy</x:v>
+      </x:c>
+      <x:c r="B2" s="2" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C2" s="29" t="n">
-        <x:v>1.847173284862183</x:v>
-      </x:c>
-      <x:c r="D2" s="29" t="n">
-        <x:v>3.1491995299925977</x:v>
-      </x:c>
-      <x:c r="E2" s="31" t="n">
+      <x:c r="C2" s="2" t="n">
+        <x:v>1.8738296801541603</x:v>
+      </x:c>
+      <x:c r="D2" s="2" t="n">
+        <x:v>3.088523429790508</x:v>
+      </x:c>
+      <x:c r="E2" s="2" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="25" t="str">
-        <x:v>15度双光束</x:v>
-      </x:c>
-      <x:c r="B3" s="27" t="n">
+      <x:c r="A3" s="2" t="str">
+        <x:v>15度Airy</x:v>
+      </x:c>
+      <x:c r="B3" s="2" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C3" s="29" t="n">
-        <x:v>2.619942371661211</x:v>
-      </x:c>
-      <x:c r="D3" s="29" t="n">
-        <x:v>31.802124579579903</x:v>
-      </x:c>
-      <x:c r="E3" s="31" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="25" t="str">
-        <x:v>联合双光束</x:v>
-      </x:c>
-      <x:c r="B4" s="27" t="n">
-        <x:v>12.5</x:v>
-      </x:c>
-      <x:c r="C4" s="29" t="n">
-        <x:v>2.708349267531435</x:v>
-      </x:c>
-      <x:c r="D4" s="29" t="n">
-        <x:v>29.71060844579701</x:v>
-      </x:c>
-      <x:c r="E4" s="31" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="25" t="str">
-        <x:v>10度Airy</x:v>
-      </x:c>
-      <x:c r="B5" s="27" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C5" s="29" t="n">
-        <x:v>1.8675697460052012</x:v>
-      </x:c>
-      <x:c r="D5" s="29" t="n">
-        <x:v>3.1376870179993603</x:v>
-      </x:c>
-      <x:c r="E5" s="31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="26" t="str">
-        <x:v>15度Airy</x:v>
-      </x:c>
-      <x:c r="B6" s="28" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C6" s="30" t="n">
-        <x:v>2.6247010749874433</x:v>
-      </x:c>
-      <x:c r="D6" s="30" t="n">
-        <x:v>32.117136899685946</x:v>
-      </x:c>
-      <x:c r="E6" s="32" t="n">
+      <x:c r="C3" s="2" t="n">
+        <x:v>3.3553823523633466</x:v>
+      </x:c>
+      <x:c r="D3" s="2" t="n">
+        <x:v>9.643590292070767</x:v>
+      </x:c>
+      <x:c r="E3" s="2" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>

--- a/modules/40_q3/figures/editable/origin_templates/data/19_Si参数可辨识性气泡图.xlsx
+++ b/modules/40_q3/figures/editable/origin_templates/data/19_Si参数可辨识性气泡图.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据" sheetId="1" r:id="R5d1ce14204794e88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据" sheetId="1" r:id="Ra7f68480fc0648f1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -286,54 +286,351 @@
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
       <x:c r="A1" s="6" t="str">
-        <x:v>拟合方案(标签)</x:v>
+        <x:v>参数(X)</x:v>
       </x:c>
       <x:c r="B1" s="6" t="str">
-        <x:v>入射角(度)(X)</x:v>
+        <x:v>入射角(度)(颜色分组)</x:v>
       </x:c>
       <x:c r="C1" s="6" t="str">
-        <x:v>RMSE(百分点)(Y)</x:v>
+        <x:v>log10相对灵敏度(Y)</x:v>
       </x:c>
       <x:c r="D1" s="6" t="str">
-        <x:v>Jacobian条件数(气泡大小)</x:v>
+        <x:v>最弱右奇异方向权重(气泡面积)</x:v>
       </x:c>
       <x:c r="E1" s="6" t="str">
-        <x:v>触边参数个数(颜色分组)</x:v>
+        <x:v>边界命中(描边)</x:v>
+      </x:c>
+      <x:c r="F1" t="str">
+        <x:v>列归一化条件数(辅助)</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="2" t="str">
-        <x:v>10度Airy</x:v>
+        <x:v>d</x:v>
       </x:c>
       <x:c r="B2" s="2" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C2" s="2" t="n">
-        <x:v>1.8738296801541603</x:v>
+        <x:v>-0.14457174436800674</x:v>
       </x:c>
       <x:c r="D2" s="2" t="n">
-        <x:v>3.088523429790508</x:v>
+        <x:v>0.3498080501606551</x:v>
       </x:c>
       <x:c r="E2" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F2" t="n">
+        <x:v>3.087893962880604</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="2" t="str">
-        <x:v>15度Airy</x:v>
+        <x:v>n3</x:v>
       </x:c>
       <x:c r="B3" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C3" s="2" t="n">
+        <x:v>-0.5661103749896975</x:v>
+      </x:c>
+      <x:c r="D3" s="2" t="n">
+        <x:v>0.18301657037934774</x:v>
+      </x:c>
+      <x:c r="E3" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F3" t="n">
+        <x:v>3.087893962880604</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>log10N</x:v>
+      </x:c>
+      <x:c r="B4" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C4" t="n">
+        <x:v>-1.947999026556184</x:v>
+      </x:c>
+      <x:c r="D4" t="n">
+        <x:v>0.3931818157503537</x:v>
+      </x:c>
+      <x:c r="E4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F4" t="n">
+        <x:v>3.087893962880604</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>log10Gamma_e</x:v>
+      </x:c>
+      <x:c r="B5" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C5" t="n">
+        <x:v>-5.4386202074066725</x:v>
+      </x:c>
+      <x:c r="D5" t="n">
+        <x:v>0.07399356370964347</x:v>
+      </x:c>
+      <x:c r="E5" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F5" t="n">
+        <x:v>3.087893962880604</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>d</x:v>
+      </x:c>
+      <x:c r="B6" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="n">
-        <x:v>3.3553823523633466</x:v>
-      </x:c>
-      <x:c r="D3" s="2" t="n">
-        <x:v>9.643590292070767</x:v>
-      </x:c>
-      <x:c r="E3" s="2" t="n">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="C6" t="n">
+        <x:v>-0.039884404320705516</x:v>
+      </x:c>
+      <x:c r="D6" t="n">
+        <x:v>0.00898986136638474</x:v>
+      </x:c>
+      <x:c r="E6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F6" t="n">
+        <x:v>9.954363116846206</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>n3</x:v>
+      </x:c>
+      <x:c r="B7" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C7" t="n">
+        <x:v>-0.5701977244532084</x:v>
+      </x:c>
+      <x:c r="D7" t="n">
+        <x:v>0.16999822019997343</x:v>
+      </x:c>
+      <x:c r="E7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F7" t="n">
+        <x:v>9.954363116846206</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>log10N</x:v>
+      </x:c>
+      <x:c r="B8" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C8" t="n">
+        <x:v>-8.534106889259487</x:v>
+      </x:c>
+      <x:c r="D8" t="n">
+        <x:v>0.459536087485736</x:v>
+      </x:c>
+      <x:c r="E8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F8" t="n">
+        <x:v>9.954363116846206</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>log10Gamma_e</x:v>
+      </x:c>
+      <x:c r="B9" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C9" t="n">
+        <x:v>-8.567441917932458</x:v>
+      </x:c>
+      <x:c r="D9" t="n">
+        <x:v>0.3614758309479058</x:v>
+      </x:c>
+      <x:c r="E9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F9" t="n">
+        <x:v>9.954363116846206</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10"/>
+      <x:c r="B10"/>
+      <x:c r="C10"/>
+      <x:c r="D10"/>
+      <x:c r="E10"/>
+      <x:c r="F10"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11"/>
+      <x:c r="B11"/>
+      <x:c r="C11"/>
+      <x:c r="D11"/>
+      <x:c r="E11"/>
+      <x:c r="F11"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12"/>
+      <x:c r="B12"/>
+      <x:c r="C12"/>
+      <x:c r="D12"/>
+      <x:c r="E12"/>
+      <x:c r="F12"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13"/>
+      <x:c r="B13"/>
+      <x:c r="C13"/>
+      <x:c r="D13"/>
+      <x:c r="E13"/>
+      <x:c r="F13"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14"/>
+      <x:c r="B14"/>
+      <x:c r="C14"/>
+      <x:c r="D14"/>
+      <x:c r="E14"/>
+      <x:c r="F14"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15"/>
+      <x:c r="B15"/>
+      <x:c r="C15"/>
+      <x:c r="D15"/>
+      <x:c r="E15"/>
+      <x:c r="F15"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16"/>
+      <x:c r="B16"/>
+      <x:c r="C16"/>
+      <x:c r="D16"/>
+      <x:c r="E16"/>
+      <x:c r="F16"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17"/>
+      <x:c r="B17"/>
+      <x:c r="C17"/>
+      <x:c r="D17"/>
+      <x:c r="E17"/>
+      <x:c r="F17"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18"/>
+      <x:c r="B18"/>
+      <x:c r="C18"/>
+      <x:c r="D18"/>
+      <x:c r="E18"/>
+      <x:c r="F18"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19"/>
+      <x:c r="B19"/>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20"/>
+      <x:c r="B20"/>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21"/>
+      <x:c r="B21"/>
+      <x:c r="C21"/>
+      <x:c r="D21"/>
+      <x:c r="E21"/>
+      <x:c r="F21"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22"/>
+      <x:c r="B22"/>
+      <x:c r="C22"/>
+      <x:c r="D22"/>
+      <x:c r="E22"/>
+      <x:c r="F22"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23"/>
+      <x:c r="B23"/>
+      <x:c r="C23"/>
+      <x:c r="D23"/>
+      <x:c r="E23"/>
+      <x:c r="F23"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24"/>
+      <x:c r="B24"/>
+      <x:c r="C24"/>
+      <x:c r="D24"/>
+      <x:c r="E24"/>
+      <x:c r="F24"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25"/>
+      <x:c r="B25"/>
+      <x:c r="C25"/>
+      <x:c r="D25"/>
+      <x:c r="E25"/>
+      <x:c r="F25"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26"/>
+      <x:c r="B26"/>
+      <x:c r="C26"/>
+      <x:c r="D26"/>
+      <x:c r="E26"/>
+      <x:c r="F26"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27"/>
+      <x:c r="B27"/>
+      <x:c r="C27"/>
+      <x:c r="D27"/>
+      <x:c r="E27"/>
+      <x:c r="F27"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28"/>
+      <x:c r="B28"/>
+      <x:c r="C28"/>
+      <x:c r="D28"/>
+      <x:c r="E28"/>
+      <x:c r="F28"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29"/>
+      <x:c r="B29"/>
+      <x:c r="C29"/>
+      <x:c r="D29"/>
+      <x:c r="E29"/>
+      <x:c r="F29"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30"/>
+      <x:c r="B30"/>
+      <x:c r="C30"/>
+      <x:c r="D30"/>
+      <x:c r="E30"/>
+      <x:c r="F30"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
